--- a/sample_data/wedstrijd-data-2026-09-05.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-05.xlsx
@@ -1351,10 +1351,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>290.411114</v>
+        <v>295.574541</v>
       </c>
       <c r="D15" t="n">
-        <v>296.225462</v>
+        <v>315.562824</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>312.732166</v>
+        <v>348.638659</v>
       </c>
       <c r="D27" t="n">
-        <v>242.406593</v>
+        <v>238.795655</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>

--- a/sample_data/wedstrijd-data-2026-09-05.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-05.xlsx
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>219.067672</v>
+        <v>246.108225</v>
       </c>
       <c r="D2" t="n">
-        <v>293.733812</v>
+        <v>330.601636</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>88.611863</v>
+        <v>99.54964200000001</v>
       </c>
       <c r="D3" t="n">
-        <v>128.526013</v>
+        <v>144.657878</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>156.479976</v>
+        <v>175.795036</v>
       </c>
       <c r="D4" t="n">
-        <v>176.802044</v>
+        <v>198.993247</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>193.375006</v>
+        <v>217.244193</v>
       </c>
       <c r="D5" t="n">
-        <v>198.934084</v>
+        <v>223.903177</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>362.543919</v>
+        <v>407.294421</v>
       </c>
       <c r="D6" t="n">
-        <v>218.480161</v>
+        <v>245.902568</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>93.233163</v>
+        <v>104.741371</v>
       </c>
       <c r="D7" t="n">
-        <v>270.686645</v>
+        <v>304.661717</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>72.825875</v>
+        <v>81.815116</v>
       </c>
       <c r="D8" t="n">
-        <v>183.929511</v>
+        <v>207.015313</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>353.769413</v>
+        <v>397.436836</v>
       </c>
       <c r="D9" t="n">
-        <v>311.931189</v>
+        <v>351.083047</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>224.918311</v>
+        <v>252.681036</v>
       </c>
       <c r="D10" t="n">
-        <v>335.450044</v>
+        <v>377.553856</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>489.248552</v>
+        <v>549.6388020000001</v>
       </c>
       <c r="D11" t="n">
-        <v>323.741037</v>
+        <v>364.3752</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>153.88235</v>
+        <v>172.876773</v>
       </c>
       <c r="D12" t="n">
-        <v>154.554427</v>
+        <v>173.953233</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>151.830491</v>
+        <v>170.571643</v>
       </c>
       <c r="D13" t="n">
-        <v>190.468845</v>
+        <v>214.375429</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>401.071397</v>
+        <v>450.577526</v>
       </c>
       <c r="D14" t="n">
-        <v>201.41273</v>
+        <v>226.692929</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>295.574541</v>
+        <v>332.058698</v>
       </c>
       <c r="D15" t="n">
-        <v>315.562824</v>
+        <v>355.170503</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>202.976653</v>
+        <v>228.031017</v>
       </c>
       <c r="D16" t="n">
-        <v>202.479578</v>
+        <v>227.893681</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>74.319114</v>
+        <v>83.492671</v>
       </c>
       <c r="D17" t="n">
-        <v>275.463957</v>
+        <v>310.038651</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>449.798473</v>
+        <v>505.319215</v>
       </c>
       <c r="D18" t="n">
-        <v>174.632749</v>
+        <v>196.551674</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>489.738244</v>
+        <v>550.18894</v>
       </c>
       <c r="D19" t="n">
-        <v>295.634994</v>
+        <v>332.741443</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>176.337464</v>
+        <v>198.103627</v>
       </c>
       <c r="D20" t="n">
-        <v>161.647237</v>
+        <v>181.936293</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>403.936905</v>
+        <v>453.796738</v>
       </c>
       <c r="D21" t="n">
-        <v>292.820792</v>
+        <v>329.57402</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>98.601769</v>
+        <v>110.772649</v>
       </c>
       <c r="D22" t="n">
-        <v>321.948349</v>
+        <v>362.357504</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>409.233199</v>
+        <v>459.746778</v>
       </c>
       <c r="D23" t="n">
-        <v>115.428774</v>
+        <v>129.916747</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>130.534523</v>
+        <v>146.647014</v>
       </c>
       <c r="D24" t="n">
-        <v>174.821938</v>
+        <v>196.764609</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>400.106872</v>
+        <v>449.493946</v>
       </c>
       <c r="D25" t="n">
-        <v>238.976249</v>
+        <v>268.97121</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>239.282632</v>
+        <v>268.818413</v>
       </c>
       <c r="D26" t="n">
-        <v>174.569927</v>
+        <v>196.480967</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>348.638659</v>
+        <v>391.672769</v>
       </c>
       <c r="D27" t="n">
-        <v>238.795655</v>
+        <v>268.76795</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>139.573944</v>
+        <v>156.802213</v>
       </c>
       <c r="D28" t="n">
-        <v>140.468112</v>
+        <v>158.098883</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>210.086308</v>
+        <v>236.01825</v>
       </c>
       <c r="D29" t="n">
-        <v>200.739277</v>
+        <v>225.934948</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>119.746288</v>
+        <v>134.527136</v>
       </c>
       <c r="D30" t="n">
-        <v>267.804178</v>
+        <v>301.417459</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>410.560624</v>
+        <v>461.238054</v>
       </c>
       <c r="D31" t="n">
-        <v>270.45092</v>
+        <v>304.396406</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
